--- a/data/信用债发行汇总_2026-09-03.xlsx
+++ b/data/信用债发行汇总_2026-09-03.xlsx
@@ -1863,7 +1863,9 @@
           <t>2.00 ~ 3.00</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="n">
+        <v>2.75</v>
+      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
           <t>珠海华发集团有限公司</t>
@@ -11564,7 +11566,11 @@
           <t>26铁道16</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2680032.IB</t>
+        </is>
+      </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
           <t>30Y</t>
@@ -11578,7 +11584,9 @@
           <t>1.58 ~ 2.58</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr"/>
+      <c r="G9" s="2" t="n">
+        <v>2.29</v>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>中国国家铁路集团有限公司</t>
@@ -11591,7 +11599,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26铁道14(柜台)</t>
+          <t>26铁道14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -13827,7 +13835,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AN21" s="2" t="inlineStr"/>
+      <c r="AN21" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -15544,7 +15554,11 @@
           <t>26铁道16</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2680032.IB</t>
+        </is>
+      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>30Y</t>
@@ -15558,7 +15572,9 @@
           <t>1.58 ~ 2.58</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
+      <c r="H9" s="2" t="n">
+        <v>2.29</v>
+      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
           <t>中国国家铁路集团有限公司</t>
@@ -15571,7 +15587,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26铁道14(柜台)</t>
+          <t>26铁道14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -17867,7 +17883,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AO21" s="2" t="inlineStr"/>
+      <c r="AO21" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -18080,7 +18098,9 @@
           <t>2.00 ~ 3.00</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr"/>
+      <c r="H23" s="2" t="n">
+        <v>2.75</v>
+      </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
           <t>珠海华发集团有限公司</t>
@@ -18261,7 +18281,9 @@
           <t>2.50 ~ 3.50</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr"/>
+      <c r="H24" s="2" t="n">
+        <v>2.9</v>
+      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t>昆明市高速公路建设开发股份有限公司</t>
@@ -18788,7 +18810,9 @@
           <t>2.00 ~ 2.45</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr"/>
+      <c r="H27" s="2" t="n">
+        <v>2.43</v>
+      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
           <t>厦门象屿金象融资租赁有限公司</t>
@@ -18941,9 +18965,7 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AO27" s="2" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AO27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -20634,7 +20656,9 @@
           <t>2.00 ~ 2.50</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr"/>
+      <c r="H37" s="2" t="n">
+        <v>2.29</v>
+      </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
           <t>广西投资集团有限公司</t>
@@ -21370,7 +21394,9 @@
           <t>1.80 ~ 2.35</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr"/>
+      <c r="H41" s="2" t="n">
+        <v>2.25</v>
+      </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
           <t>浙商中拓集团股份有限公司</t>
@@ -21551,7 +21577,9 @@
           <t>1.80 ~ 2.50</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr"/>
+      <c r="H42" s="2" t="n">
+        <v>2.14</v>
+      </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
           <t>厦门海沧投资集团有限公司</t>
@@ -21696,9 +21724,7 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AO42" s="2" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AO42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -21734,7 +21760,9 @@
           <t>1.70 ~ 2.70</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr"/>
+      <c r="H43" s="2" t="n">
+        <v>2.09</v>
+      </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
           <t>厦门海翼集团有限公司</t>
@@ -21879,9 +21907,7 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AO43" s="2" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AO43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -22458,7 +22484,9 @@
           <t>1.80 ~ 2.30</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr"/>
+      <c r="H47" s="2" t="n">
+        <v>2.29</v>
+      </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
           <t>广西投资集团有限公司</t>
@@ -22603,9 +22631,7 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AO47" s="2" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AO47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -23373,7 +23399,9 @@
           <t>1.60 ~ 2.60</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr"/>
+      <c r="H52" s="2" t="n">
+        <v>2.05</v>
+      </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
           <t>晋能控股电力集团有限公司</t>
@@ -23528,22 +23556,22 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>09-01 18:00</t>
+          <t>09-01 19:00</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>26璧山城投MTN001</t>
+          <t>GC甬轨Y2</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>102683469.IB</t>
+          <t>245959.SH</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
@@ -23551,40 +23579,40 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>重庆市璧山区城市建设投资有限公司</t>
+          <t>宁波市轨道交通集团有限公司</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>重庆市-璧山区</t>
+          <t>浙江省-宁波市</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>26璧山01</t>
+          <t>26甬轨Y4</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>4.43Y</t>
+          <t>4.79Y+N</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>2.0175</t>
+          <t>1.9236</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
@@ -23594,23 +23622,19 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr"/>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>国投证券股份有限公司,财信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="S53" s="2" t="inlineStr">
-        <is>
-          <t>重庆两山建设投资集团有限公司</t>
-        </is>
-      </c>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司,华泰联合证券有限责任公司,甬兴证券有限公司</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr"/>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -23620,12 +23644,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>重庆市璧山区城市建设投资有限公司2026年度第一期中期票据</t>
+          <t>宁波市轨道交通集团有限公司2026年面向专业投资者公开发行碳中和绿色可续期公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
@@ -23635,25 +23659,21 @@
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>2031-09-02</t>
+          <t>2031-09-03</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr"/>
-      <c r="AA53" s="2" t="inlineStr">
+      <c r="AA53" s="2" t="inlineStr"/>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AB53" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
           <t>城投</t>
@@ -23661,7 +23681,7 @@
       </c>
       <c r="AE53" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AF53" s="2" t="inlineStr">
@@ -23671,12 +23691,12 @@
       </c>
       <c r="AG53" s="2" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AH53" s="2" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AI53" s="2" t="inlineStr">
@@ -23687,17 +23707,17 @@
       <c r="AJ53" s="2" t="inlineStr"/>
       <c r="AK53" s="2" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AL53" s="2" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AM53" s="2" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AN53" s="2" t="inlineStr">
@@ -23715,63 +23735,63 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>09-01 19:00</t>
+          <t>09-01 18:00</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>GC甬轨Y2</t>
+          <t>26西青经开MTN001</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>245959.SH</t>
+          <t>102683504.IB</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H54" s="2" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>宁波市轨道交通集团有限公司</t>
+          <t>天津市西青经济开发集团有限公司</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>浙江省-宁波市</t>
+          <t>天津市-西青区</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>26甬轨Y4</t>
+          <t>24武清经开MTN006</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>4.79Y+N</t>
+          <t>2.83Y</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1.9236</t>
+          <t>2.0125</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
@@ -23781,19 +23801,19 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr"/>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司,华泰联合证券有限责任公司,甬兴证券有限公司</t>
+          <t>兴业银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr"/>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -23803,12 +23823,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>宁波市轨道交通集团有限公司2026年面向专业投资者公开发行碳中和绿色可续期公司债券(第一期)(品种二)</t>
+          <t>天津市西青经济开发集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
@@ -23818,29 +23838,37 @@
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>2031-09-03</t>
-        </is>
-      </c>
-      <c r="Z54" s="2" t="inlineStr"/>
-      <c r="AA54" s="2" t="inlineStr"/>
+          <t>2029-09-02</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AE54" s="2" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF54" s="2" t="inlineStr">
@@ -23850,17 +23878,17 @@
       </c>
       <c r="AG54" s="2" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AH54" s="2" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AI54" s="2" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AJ54" s="2" t="inlineStr"/>
@@ -23871,12 +23899,12 @@
       </c>
       <c r="AL54" s="2" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AM54" s="2" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AN54" s="2" t="inlineStr">
@@ -23899,58 +23927,58 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>26西青经开MTN001</t>
+          <t>26璧山城投MTN001</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>102683504.IB</t>
+          <t>102683469.IB</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>天津市西青经济开发集团有限公司</t>
+          <t>重庆市璧山区城市建设投资有限公司</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>天津市-西青区</t>
+          <t>重庆市-璧山区</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>24武清经开MTN006</t>
+          <t>26璧山01</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>2.83Y</t>
+          <t>4.43Y</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>2.0125</t>
+          <t>2.0175</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
@@ -23960,16 +23988,20 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr"/>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中信银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="S55" s="2" t="inlineStr"/>
+          <t>国投证券股份有限公司,财信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>重庆两山建设投资集团有限公司</t>
+        </is>
+      </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
           <t>中期票据</t>
@@ -23987,7 +24019,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>天津市西青经济开发集团有限公司2026年度第一期中期票据</t>
+          <t>重庆市璧山区城市建设投资有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
@@ -23997,14 +24029,10 @@
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>2029-09-02</t>
-        </is>
-      </c>
-      <c r="Z55" s="2" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr"/>
       <c r="AA55" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
@@ -24012,7 +24040,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -24022,7 +24050,7 @@
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AE55" s="2" t="inlineStr">
@@ -24037,23 +24065,23 @@
       </c>
       <c r="AG55" s="2" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AH55" s="2" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AI55" s="2" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AJ55" s="2" t="inlineStr"/>
       <c r="AK55" s="2" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AL55" s="2" t="inlineStr">
